--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationadministrationBase.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-medicationadministrationBase.xlsx
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -702,7 +702,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -796,7 +796,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -893,7 +893,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -955,7 +955,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -979,7 +979,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -989,7 +989,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>医薬品</t>
@@ -1009,7 +1009,7 @@
     <t>投与可能な物質または製品を識別するコード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1027,7 +1027,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1052,7 +1052,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1077,7 +1077,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1187,7 +1187,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1199,7 +1199,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1227,7 +1227,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1242,7 +1242,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1270,7 +1270,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1295,7 +1295,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1383,7 +1383,7 @@
     <t>薬剤が体内に入るか、体表面に塗布される場所を示すコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1404,7 +1404,7 @@
     <t>治療薬剤を被験者の体内あるいは体表面へ投与する生理学的ルートや経路を記述する符号化された概念</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1428,7 +1428,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1440,7 +1440,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1463,7 +1463,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>時間当たりの投与量</t>
@@ -1484,7 +1484,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1829,7 +1829,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
